--- a/Farm/Assets/Configs/shop.xlsx
+++ b/Farm/Assets/Configs/shop.xlsx
@@ -37,7 +37,7 @@
     <t>#商店</t>
   </si>
   <si>
-    <t>{"format":"map","key":["id"]}</t>
+    <t>{"format":"list"}</t>
   </si>
   <si>
     <t>商品id</t>
